--- a/data/0493_Frachtenrechner_KEP_DATA.xlsx
+++ b/data/0493_Frachtenrechner_KEP_DATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christineklein/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00B9789C-A4DD-E245-8460-51E5F461B66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{558CCD65-19B5-2E41-87FF-8A2134EBC186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34560" yWindow="2080" windowWidth="34560" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34560" yWindow="1940" windowWidth="34560" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="adds" sheetId="1" r:id="rId1"/>
@@ -1551,7 +1551,6 @@
     <definedName name="Zone">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2651,7 +2650,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.3</v>
+        <v>0.30499999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2659,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.3</v>
+        <v>0.30499999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2667,7 +2666,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.3</v>
+        <v>0.30499999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2675,7 +2674,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.3</v>
+        <v>0.30499999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2683,7 +2682,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -2691,7 +2690,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -2699,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2707,7 +2706,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -2715,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -2723,7 +2722,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -2731,7 +2730,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -2739,7 +2738,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.48499999999999999</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
   </sheetData>
